--- a/sources/table_normalization/xlsx/economy-table61.xlsx
+++ b/sources/table_normalization/xlsx/economy-table61.xlsx
@@ -118,10 +118,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="168" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ [$₽-419]_-;\-* #,##0.00\ [$₽-419]_-;_-* &quot;-&quot;??\ [$₽-419]_-;_-@_-"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -494,7 +494,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -506,7 +506,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -518,7 +518,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -536,7 +536,7 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -595,58 +595,43 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -662,14 +647,29 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="4" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -982,7 +982,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>1181100</xdr:colOff>
+          <xdr:colOff>647700</xdr:colOff>
           <xdr:row>30</xdr:row>
           <xdr:rowOff>342900</xdr:rowOff>
         </xdr:to>
@@ -1308,27 +1308,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="48" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="23"/>
       <c r="F1" s="24"/>
       <c r="G1" s="25"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
       <c r="J1" s="37"/>
-      <c r="K1" s="50" t="s">
+      <c r="K1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="50"/>
+      <c r="L1" s="58"/>
     </row>
     <row r="2" spans="1:12" ht="17">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
@@ -1340,46 +1340,46 @@
       <c r="H2" s="4"/>
       <c r="I2" s="38"/>
       <c r="J2" s="38"/>
-      <c r="K2" s="49" t="s">
+      <c r="K2" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="49"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="1:12" ht="46.5">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="59" t="s">
+      <c r="I3" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="60" t="s">
+      <c r="K3" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="60" t="s">
+      <c r="L3" s="55" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       <c r="F31" s="34"/>
       <c r="G31" s="35"/>
       <c r="H31" s="36"/>
-      <c r="I31" s="61" t="s">
+      <c r="I31" s="56" t="s">
         <v>24</v>
       </c>
       <c r="J31" s="45"/>
